--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NEW_MEXICO_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NEW_MEXICO_2019.xlsx
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C150">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C228">
@@ -6331,7 +6331,7 @@
         <v>57</v>
       </c>
       <c r="D332">
-        <v>0.009364218827008379</v>
+        <v>0.009364218827008381</v>
       </c>
     </row>
     <row r="333">
@@ -10633,7 +10633,7 @@
         <v>57</v>
       </c>
       <c r="D571">
-        <v>0.009364218827008379</v>
+        <v>0.009364218827008381</v>
       </c>
     </row>
     <row r="572">
